--- a/Hotel Booking.xlsx
+++ b/Hotel Booking.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2440638_cognizant_com/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2473903_cognizant_com/Documents/Desktop/Tekstac-functional testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7153AA64-D588-4525-B62D-6608634FC5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{7153AA64-D588-4525-B62D-6608634FC5E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDF889F9-8C6A-4BDD-9A2A-4FD101BA5EA9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="5" r:id="rId1"/>
@@ -315,9 +315,6 @@
     <t>High</t>
   </si>
   <si>
-    <t>Venkata Kiran</t>
-  </si>
-  <si>
     <t>New</t>
   </si>
   <si>
@@ -355,13 +352,16 @@
   </si>
   <si>
     <t>Hotel booking functionality for Raj Travels</t>
+  </si>
+  <si>
+    <t>Bhargav Raghuram</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -469,6 +469,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -759,9 +763,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -778,7 +782,7 @@
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -795,7 +799,7 @@
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -812,7 +816,7 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -829,7 +833,7 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -846,7 +850,7 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>0</v>
@@ -865,7 +869,7 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
@@ -884,7 +888,7 @@
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5" t="s">
@@ -903,7 +907,7 @@
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5" t="s">
@@ -922,7 +926,7 @@
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
@@ -941,7 +945,7 @@
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
@@ -960,7 +964,7 @@
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
@@ -979,7 +983,7 @@
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -996,7 +1000,7 @@
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1013,7 +1017,7 @@
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1030,7 +1034,7 @@
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1047,7 +1051,7 @@
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1064,7 +1068,7 @@
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1081,7 +1085,7 @@
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1098,7 +1102,7 @@
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1124,16 +1128,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20.7265625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" customWidth="1"/>
-    <col min="4" max="4" width="59.5703125" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" customWidth="1"/>
+    <col min="4" max="4" width="59.54296875" customWidth="1"/>
+    <col min="5" max="5" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1150,7 +1154,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1167,7 +1171,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1184,7 +1188,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1201,7 +1205,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1227,21 +1231,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="3" width="44.7109375" customWidth="1"/>
-    <col min="4" max="4" width="43.85546875" customWidth="1"/>
-    <col min="5" max="5" width="55.42578125" customWidth="1"/>
-    <col min="6" max="6" width="43.140625" customWidth="1"/>
-    <col min="7" max="7" width="40.140625" customWidth="1"/>
-    <col min="8" max="8" width="20.140625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" style="10" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" customWidth="1"/>
+    <col min="1" max="2" width="28.7265625" customWidth="1"/>
+    <col min="3" max="3" width="44.7265625" customWidth="1"/>
+    <col min="4" max="4" width="43.81640625" customWidth="1"/>
+    <col min="5" max="5" width="55.453125" customWidth="1"/>
+    <col min="6" max="6" width="43.1796875" customWidth="1"/>
+    <col min="7" max="7" width="40.1796875" customWidth="1"/>
+    <col min="8" max="8" width="20.1796875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="21.54296875" style="10" customWidth="1"/>
+    <col min="10" max="10" width="17.26953125" style="10" customWidth="1"/>
+    <col min="11" max="11" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
@@ -1273,7 +1277,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="29.1">
+    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>13</v>
       </c>
@@ -1305,7 +1309,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="29.1">
+    <row r="3" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
@@ -1337,7 +1341,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>17</v>
       </c>
@@ -1369,7 +1373,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>17</v>
       </c>
@@ -1401,7 +1405,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="29.1">
+    <row r="6" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
         <v>20</v>
       </c>
@@ -1433,7 +1437,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>20</v>
       </c>
@@ -1465,7 +1469,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>23</v>
       </c>
@@ -1497,7 +1501,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>76</v>
       </c>
@@ -1511,22 +1515,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="42.7109375" customWidth="1"/>
+    <col min="1" max="1" width="17.26953125" customWidth="1"/>
+    <col min="2" max="2" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="42.7265625" customWidth="1"/>
     <col min="4" max="4" width="23" customWidth="1"/>
-    <col min="5" max="5" width="40.85546875" customWidth="1"/>
+    <col min="5" max="5" width="40.81640625" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" customWidth="1"/>
-    <col min="8" max="8" width="19.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.1796875" customWidth="1"/>
+    <col min="8" max="8" width="19.1796875" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" customWidth="1"/>
+    <col min="10" max="10" width="18.26953125" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>77</v>
       </c>
@@ -1561,7 +1565,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="29.1">
+    <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1584,19 +1588,19 @@
         <v>89</v>
       </c>
       <c r="H2" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I2" s="8">
+        <v>46079</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I2" s="8">
-        <v>45910</v>
-      </c>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="K2" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="43.5">
+    </row>
+    <row r="3" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -1604,7 +1608,7 @@
         <v>57</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>87</v>
@@ -1613,25 +1617,25 @@
         <v>54</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>89</v>
       </c>
       <c r="H3" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I3" s="8">
+        <v>46080</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I3" s="8">
-        <v>45910</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="K3" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="29.1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -1639,7 +1643,7 @@
         <v>75</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>87</v>
@@ -1654,16 +1658,16 @@
         <v>89</v>
       </c>
       <c r="H4" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I4" s="8">
+        <v>46081</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="8">
-        <v>45910</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="K4" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -1675,37 +1679,37 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="3"/>
+    <col min="1" max="1" width="8.7265625" style="3"/>
     <col min="2" max="2" width="19" style="10" customWidth="1"/>
     <col min="3" max="3" width="45" style="10" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" style="10" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="18.7265625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="19.26953125" style="10" customWidth="1"/>
     <col min="6" max="6" width="20" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1">
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>100</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>27</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -1713,7 +1717,7 @@
         <v>16</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>13</v>
@@ -1725,7 +1729,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -1733,7 +1737,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>13</v>
@@ -1745,7 +1749,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1753,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>17</v>
@@ -1765,7 +1769,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -1773,7 +1777,7 @@
         <v>16</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>17</v>
@@ -1785,7 +1789,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -1793,7 +1797,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>20</v>
@@ -1805,7 +1809,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -1813,7 +1817,7 @@
         <v>16</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>20</v>
@@ -1825,7 +1829,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -1833,7 +1837,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>23</v>
